--- a/Result/profitability/5609.xlsx
+++ b/Result/profitability/5609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.38</v>
       </c>
       <c r="M2" t="n">
-        <v>1.64125</v>
+        <v>1.7575</v>
       </c>
       <c r="N2" t="n">
-        <v>13.21</v>
+        <v>13.12125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.53</v>
       </c>
       <c r="M3" t="n">
-        <v>1.5275</v>
+        <v>1.6175</v>
       </c>
       <c r="N3" t="n">
-        <v>13.675</v>
+        <v>13.59625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.74</v>
       </c>
       <c r="M4" t="n">
-        <v>1.41375</v>
+        <v>1.50625</v>
       </c>
       <c r="N4" t="n">
-        <v>13.89625</v>
+        <v>13.71875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.3</v>
       </c>
       <c r="M5" t="n">
-        <v>1.2475</v>
+        <v>1.215</v>
       </c>
       <c r="N5" t="n">
-        <v>13.58125</v>
+        <v>13.305</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.26</v>
       </c>
       <c r="M6" t="n">
-        <v>0.95125</v>
+        <v>1.01375</v>
       </c>
       <c r="N6" t="n">
-        <v>14.305</v>
+        <v>13.99625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.64</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7975</v>
+        <v>0.8600000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>14.98</v>
+        <v>14.87125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.63</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6425</v>
+        <v>0.7312500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>15.69625</v>
+        <v>15.4875</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5609</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>9589</v>
+      </c>
+      <c r="D75" t="n">
+        <v>8442</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1147</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="G75" t="n">
+        <v>387</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.03%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>20</v>
+      </c>
+      <c r="J75" t="n">
+        <v>407</v>
+      </c>
+      <c r="K75" t="n">
+        <v>334</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.2175</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.7100000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.4277108433734942</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1224340175953079</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.2599999999999998</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.09885931558935357</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.209999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1558533145275035</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
